--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CD4BFF-F519-4860-A4E3-AF92DC467A14}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D0384C4-658D-4E7C-BAA7-69BCFBD7C921}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,6 +267,36 @@
   </si>
   <si>
     <t>Spent some time studying and also took time to chill.</t>
+  </si>
+  <si>
+    <t>Had online classes .</t>
+  </si>
+  <si>
+    <t>Spent the day attending online classes and working on study and coding. Felt a little tired but had a good day overall.</t>
+  </si>
+  <si>
+    <t>Studied for upcoming midterm exams.</t>
+  </si>
+  <si>
+    <t>Travelling back to university.</t>
+  </si>
+  <si>
+    <t>Had my first exam today.</t>
+  </si>
+  <si>
+    <t>Second exam done</t>
+  </si>
+  <si>
+    <t>Third exam done.</t>
+  </si>
+  <si>
+    <t>Prepared for next two exams.</t>
+  </si>
+  <si>
+    <t>Fourth exam done</t>
+  </si>
+  <si>
+    <t>All papers done.</t>
   </si>
 </sst>
 </file>
@@ -3529,290 +3559,602 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>20</v>
+      </c>
+      <c r="D60" s="14">
+        <v>60</v>
+      </c>
+      <c r="E60" s="14">
+        <v>30</v>
+      </c>
+      <c r="F60" s="14">
+        <v>400</v>
+      </c>
+      <c r="G60" s="14">
+        <v>5</v>
+      </c>
+      <c r="H60" s="14">
+        <v>30</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B61" s="14">
+        <v>420</v>
+      </c>
+      <c r="C61" s="14">
+        <v>20</v>
+      </c>
+      <c r="D61" s="14">
+        <v>90</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>300</v>
+      </c>
+      <c r="G61" s="14">
+        <v>5</v>
+      </c>
+      <c r="H61" s="14">
+        <v>60</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B62" s="14">
+        <v>420</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>120</v>
+      </c>
+      <c r="E62" s="14">
+        <v>60</v>
+      </c>
+      <c r="F62" s="14">
+        <v>250</v>
+      </c>
+      <c r="G62" s="14">
+        <v>4</v>
+      </c>
+      <c r="H62" s="14">
+        <v>60</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B63" s="14">
+        <v>480</v>
+      </c>
+      <c r="C63" s="14">
+        <v>20</v>
+      </c>
+      <c r="D63" s="14">
+        <v>180</v>
+      </c>
+      <c r="E63" s="14">
+        <v>30</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>60</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B64" s="14">
+        <v>480</v>
+      </c>
+      <c r="C64" s="14">
+        <v>20</v>
+      </c>
+      <c r="D64" s="14">
+        <v>180</v>
+      </c>
+      <c r="E64" s="14">
+        <v>30</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>60</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B65" s="14">
+        <v>420</v>
+      </c>
+      <c r="C65" s="14">
+        <v>20</v>
+      </c>
+      <c r="D65" s="14">
+        <v>0</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>120</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>880</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B66" s="14">
+        <v>420</v>
+      </c>
+      <c r="C66" s="14">
+        <v>20</v>
+      </c>
+      <c r="D66" s="14">
+        <v>60</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>0</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>940</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>20</v>
+      </c>
+      <c r="D67" s="14">
+        <v>120</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>30</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B68" s="14">
+        <v>420</v>
+      </c>
+      <c r="C68" s="14">
+        <v>20</v>
+      </c>
+      <c r="D68" s="14">
+        <v>120</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>30</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B69" s="14">
+        <v>420</v>
+      </c>
+      <c r="C69" s="14">
+        <v>20</v>
+      </c>
+      <c r="D69" s="14">
+        <v>120</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>30</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B70" s="14">
+        <v>480</v>
+      </c>
+      <c r="C70" s="14">
+        <v>20</v>
+      </c>
+      <c r="D70" s="14">
+        <v>180</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>60</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B71" s="14">
+        <v>420</v>
+      </c>
+      <c r="C71" s="14">
+        <v>20</v>
+      </c>
+      <c r="D71" s="14">
+        <v>120</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>30</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>20</v>
+      </c>
+      <c r="D72" s="14">
+        <v>120</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>30</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D0384C4-658D-4E7C-BAA7-69BCFBD7C921}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E65BED4-B525-469E-A7EC-FB0D1D8DD5E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4156,27 +4156,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+    <row r="73" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B73" s="14">
+        <v>480</v>
+      </c>
+      <c r="C73" s="14">
+        <v>20</v>
+      </c>
+      <c r="D73" s="14">
+        <v>30</v>
+      </c>
+      <c r="E73" s="14">
+        <v>60</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>60</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="322" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E65BED4-B525-469E-A7EC-FB0D1D8DD5E7}"/>
+  <xr:revisionPtr revIDLastSave="365" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D96C3E-B1F5-43D3-BBEE-51622C998F16}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>All papers done.</t>
+  </si>
+  <si>
+    <t>Had a very chill day with plenty of rest and some free time. Did a little studying as well.</t>
   </si>
 </sst>
 </file>
@@ -4202,71 +4205,143 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+    <row r="74" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B74" s="14">
+        <v>420</v>
+      </c>
+      <c r="C74" s="14">
+        <v>20</v>
+      </c>
+      <c r="D74" s="14">
+        <v>60</v>
+      </c>
+      <c r="E74" s="14">
+        <v>30</v>
+      </c>
+      <c r="F74" s="14">
+        <v>400</v>
+      </c>
+      <c r="G74" s="14">
+        <v>5</v>
+      </c>
+      <c r="H74" s="14">
+        <v>30</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" ref="I74:I137" si="2">IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" ref="J74:J137" si="3">IF(I74="","",1440-I74)</f>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B75" s="14">
+        <v>480</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>180</v>
+      </c>
+      <c r="E75" s="14">
+        <v>120</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>60</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B76" s="14">
+        <v>420</v>
+      </c>
+      <c r="C76" s="14">
+        <v>20</v>
+      </c>
+      <c r="D76" s="14">
+        <v>120</v>
+      </c>
+      <c r="E76" s="14">
+        <v>60</v>
+      </c>
+      <c r="F76" s="14">
+        <v>250</v>
+      </c>
+      <c r="G76" s="14">
+        <v>4</v>
+      </c>
+      <c r="H76" s="14">
+        <v>60</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D96C3E-B1F5-43D3-BBEE-51622C998F16}"/>
+  <xr:revisionPtr revIDLastSave="393" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{456BB769-A83E-41E1-A05D-09082F3BD5AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4343,49 +4343,97 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+    <row r="77" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B77" s="14">
+        <v>420</v>
+      </c>
+      <c r="C77" s="14">
+        <v>20</v>
+      </c>
+      <c r="D77" s="14">
+        <v>90</v>
+      </c>
+      <c r="E77" s="14">
+        <v>60</v>
+      </c>
+      <c r="F77" s="14">
+        <v>300</v>
+      </c>
+      <c r="G77" s="14">
+        <v>6</v>
+      </c>
+      <c r="H77" s="14">
+        <v>60</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B78" s="14">
+        <v>420</v>
+      </c>
+      <c r="C78" s="14">
+        <v>20</v>
+      </c>
+      <c r="D78" s="14">
+        <v>60</v>
+      </c>
+      <c r="E78" s="14">
+        <v>30</v>
+      </c>
+      <c r="F78" s="14">
+        <v>400</v>
+      </c>
+      <c r="G78" s="14">
+        <v>7</v>
+      </c>
+      <c r="H78" s="14">
+        <v>30</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{456BB769-A83E-41E1-A05D-09082F3BD5AE}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FADB2F9-FDD3-4CF9-B52F-AB3A74FBAEE6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>Had a very chill day with plenty of rest and some free time. Did a little studying as well.</t>
+  </si>
+  <si>
+    <t>Had a relaxed Saturday with one lab. Spent some time studying and also took time to chill.</t>
   </si>
 </sst>
 </file>
@@ -4435,27 +4438,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+    <row r="79" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B79" s="14">
+        <v>420</v>
+      </c>
+      <c r="C79" s="14">
+        <v>20</v>
+      </c>
+      <c r="D79" s="14">
+        <v>60</v>
+      </c>
+      <c r="E79" s="14">
+        <v>30</v>
+      </c>
+      <c r="F79" s="14">
+        <v>100</v>
+      </c>
+      <c r="G79" s="14">
+        <v>2</v>
+      </c>
+      <c r="H79" s="14">
+        <v>60</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="408" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FADB2F9-FDD3-4CF9-B52F-AB3A74FBAEE6}"/>
+  <xr:revisionPtr revIDLastSave="424" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{308572A9-57E7-4C8F-980E-8593323A43A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4484,27 +4484,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+    <row r="80" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B80" s="14">
+        <v>480</v>
+      </c>
+      <c r="C80" s="14">
+        <v>30</v>
+      </c>
+      <c r="D80" s="14">
+        <v>180</v>
+      </c>
+      <c r="E80" s="14">
+        <v>120</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0</v>
+      </c>
+      <c r="G80" s="14">
+        <v>0</v>
+      </c>
+      <c r="H80" s="14">
+        <v>60</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="424" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{308572A9-57E7-4C8F-980E-8593323A43A5}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20BF0D58-97E9-46C5-A0E7-688E97B2A987}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>Had a relaxed Saturday with one lab. Spent some time studying and also took time to chill.</t>
+  </si>
+  <si>
+    <t>Had a relax day with plenty of rest and some free time. Did a little studying as well.</t>
+  </si>
+  <si>
+    <t>Spent the day attending  classes and working on study and coding. Felt a little tired but had a good day overall.</t>
   </si>
 </sst>
 </file>
@@ -4530,71 +4536,143 @@
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+    <row r="81" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B81" s="14">
+        <v>480</v>
+      </c>
+      <c r="C81" s="14">
+        <v>30</v>
+      </c>
+      <c r="D81" s="14">
+        <v>180</v>
+      </c>
+      <c r="E81" s="14">
+        <v>120</v>
+      </c>
+      <c r="F81" s="14">
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <v>60</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B82" s="14">
+        <v>420</v>
+      </c>
+      <c r="C82" s="14">
+        <v>20</v>
+      </c>
+      <c r="D82" s="14">
+        <v>90</v>
+      </c>
+      <c r="E82" s="14">
+        <v>30</v>
+      </c>
+      <c r="F82" s="14">
+        <v>300</v>
+      </c>
+      <c r="G82" s="14">
+        <v>5</v>
+      </c>
+      <c r="H82" s="14">
+        <v>30</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B83" s="14">
+        <v>420</v>
+      </c>
+      <c r="C83" s="14">
+        <v>20</v>
+      </c>
+      <c r="D83" s="14">
+        <v>120</v>
+      </c>
+      <c r="E83" s="14">
+        <v>20</v>
+      </c>
+      <c r="F83" s="14">
+        <v>250</v>
+      </c>
+      <c r="G83" s="14">
+        <v>4</v>
+      </c>
+      <c r="H83" s="14">
+        <v>30</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20BF0D58-97E9-46C5-A0E7-688E97B2A987}"/>
+  <xr:revisionPtr revIDLastSave="480" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7E15EC-9AE0-4C68-88C6-C5D24439609C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4674,27 +4674,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+    <row r="84" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B84" s="14">
+        <v>420</v>
+      </c>
+      <c r="C84" s="14">
+        <v>20</v>
+      </c>
+      <c r="D84" s="14">
+        <v>60</v>
+      </c>
+      <c r="E84" s="14">
+        <v>30</v>
+      </c>
+      <c r="F84" s="14">
+        <v>300</v>
+      </c>
+      <c r="G84" s="14">
+        <v>6</v>
+      </c>
+      <c r="H84" s="14">
+        <v>30</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="480" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7E15EC-9AE0-4C68-88C6-C5D24439609C}"/>
+  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DC8B3C6-C334-4FD5-8C65-21B329D13EC9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4720,49 +4720,97 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+    <row r="85" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B85" s="14">
+        <v>420</v>
+      </c>
+      <c r="C85" s="14">
+        <v>20</v>
+      </c>
+      <c r="D85" s="14">
+        <v>60</v>
+      </c>
+      <c r="E85" s="14">
+        <v>30</v>
+      </c>
+      <c r="F85" s="14">
+        <v>350</v>
+      </c>
+      <c r="G85" s="14">
+        <v>7</v>
+      </c>
+      <c r="H85" s="14">
+        <v>30</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="13">
+        <v>46326</v>
+      </c>
+      <c r="B86" s="14">
+        <v>420</v>
+      </c>
+      <c r="C86" s="14">
+        <v>20</v>
+      </c>
+      <c r="D86" s="14">
+        <v>60</v>
+      </c>
+      <c r="E86" s="14">
+        <v>30</v>
+      </c>
+      <c r="F86" s="14">
+        <v>200</v>
+      </c>
+      <c r="G86" s="14">
+        <v>4</v>
+      </c>
+      <c r="H86" s="14">
+        <v>30</v>
+      </c>
+      <c r="I86" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J86" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
-      <c r="N86" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M86" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N86" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="13"/>

--- a/12624479(CAP776).xlsx
+++ b/12624479(CAP776).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DC8B3C6-C334-4FD5-8C65-21B329D13EC9}"/>
+  <xr:revisionPtr revIDLastSave="523" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A72EF5C-8040-41F9-A265-8F66C501E5FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4812,27 +4812,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="13"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="15" t="str">
+    <row r="87" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="13">
+        <v>46327</v>
+      </c>
+      <c r="B87" s="14">
+        <v>480</v>
+      </c>
+      <c r="C87" s="14">
+        <v>30</v>
+      </c>
+      <c r="D87" s="14">
+        <v>120</v>
+      </c>
+      <c r="E87" s="14">
+        <v>60</v>
+      </c>
+      <c r="F87" s="14">
+        <v>0</v>
+      </c>
+      <c r="G87" s="14">
+        <v>0</v>
+      </c>
+      <c r="H87" s="14">
+        <v>60</v>
+      </c>
+      <c r="I87" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J87" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
-      <c r="N87" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K87" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L87" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M87" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N87" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="13"/>
